--- a/신고신저가_20260819.xlsx
+++ b/신고신저가_20260819.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 이란·호르무즈 긴장이 유가를 브렌트 90달러로 밀어 올린 동시에 미 30년물 금리가 5.32%로 2007년 이후 최고를 찍으면서, 네 시장이 같은 두 재료로 똑같이 갈라졌다. 원유가 매출인 쪽은 신고가로, 원유가 비용이거나 금리에 눌리는 쪽은 신저가로 이동했다. 지수 낙폭은 일본이 가장 컸지만 명단이 말하는 이야기는 붕괴가 아니라 교체다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/18): 나스닥이 1.33% 빠진 하루였는데 신고가는 55종, 신저가는 14종으로 오히려 폭이 넓어졌다. 갈라진 축이 선명하다 — 새로 신고가에 들어온 31종 가운데 에너지가 8종으로 엑손모빌 2.5%를 필두로 EOG·오빈티브 같은 생산업체와 타가리소스·ONEOK 같은 미드스트림이 함께 올라왔고, 길리어드·애브트·암젠 등 헬스케어 10종과 노스롭그루먼·록히드마틴 방산이 뒤를 받쳤다. 반대로 새 신저가 9종은 성격이 하나로 묶인다. 왓츠코와 레녹스, 매디슨에어 등 공조·기계가 5종, 마틴마리에타와 CRH 골재가 2종으로 전부 금리에 목이 눌리는 건설 사슬이다. 섹터 ETF에서도 에너지 1.8%와 헬스케어 1.6%가 오른 반면 테크는 2.5% 밀려, 이날 매도가 시장 전체가 아니라 고멀티플과 금리민감에 집중됐음을 보여준다. 탈렌에너지가 11% 급락한 것은 9.8억달러 증자에 따른 희석 우려라는 개별 사정이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/18): 닛케이가 2.54% 떨어진 67,460으로 6거래일 만에 반락해 이날 네 시장 중 낙폭이 가장 컸다. 다만 무너진 곳이 정해져 있어서, 전기·정밀 업종이 3.8% 밀린 반면 에너지자원은 4.6% 올랐다. 신규 신고가는 치바은행과 시즈오카파이낸셜 두 지방은행이고 신규 신저가는 미쓰비시지쇼와 미쓰이부동산 두 부동산이라, 10년물 2.945%라는 같은 숫자가 은행에는 연료이고 부동산에는 독이라는 구도가 전 거래일보다 한층 굵어졌다. 부동산 업종은 한 달 새 6.9% 빠져 올해 유일한 마이너스 업종이 됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/18): 항셍은 보합이었지만 항셍테크가 0.90% 밀려 연초 대비 13.7% 손실이라는 중화권 최약 지위를 이어갔다. 오늘 명단의 핵심은 유가가 비용으로 작동한 자리다 — 새 신저가 4종 가운데 중국동방항공이 4.2% 떨어지며 중국남방항공과 나란히 들어왔고, 이 둘은 브렌트 강세의 직접 피해자다. 반대편 신규 신고가는 위탁개발생산 두 종목으로, 우시XDC가 7.5% 오르며 우시바이오로직스와 함께 신약목록 편입 기대를 타고 올랐다. 해운 4종은 신고가를 유지했는데 호르무즈 운임 강세의 연장으로 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/18): 상해종합이 0.19% 올라 3,990으로 4,000선 문턱에 다시 붙었지만 CSI300은 0.32% 내려 지수 간 방향이 갈렸다. 신고가 쪽에서는 캉룽화청이 일라이릴리 비만치료제 위탁생산을 따내며 홍콩 우시 계열과 같은 흐름을 탔고, 적외선 센서업체 레이턴테크놀로지가 3.6% 올랐다. 주목할 것은 네트워크 장비업체 루이제네트워크로, 장중 신고가를 찍고도 7.4% 급락 마감해 AI연산 관련주에서 차익실현이 나온 자리를 그대로 보여줬다. 신에너지차 싸이리스는 판매 급감 여진으로 A주와 H주 양쪽에서 동시에 신저가를 냈다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①브렌트가 90달러 위에 머무는지 — 에너지 신고가 무더기가 이익 재평가인지 지정학 프리미엄인지는 유가가 되돌려질 때 갈린다 ②미 30년물 5.32%가 더 오르는지 — 테크와 건자재의 하락이 같은 뿌리라서, 금리가 멈추면 둘이 같이 멈춘다 ③공조·골재 신저가 무더기가 주택 수요 둔화인지 데이터센터 냉각 기대의 되돌림인지 — 왓츠코·레녹스처럼 주택 비중이 큰 쪽과 매디슨에어처럼 산업·데이터센터 비중이 큰 쪽이 앞으로 갈라지는지가 단서다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 오늘은 유가가 같은 날 정반대로 작동한 짝이 교재다. 엑손모빌·EOG 같은 생산업체에게 원유는 파는 물건이라 가격 P가 곧 매출이 되는데, 생산량 Q와 채굴비용 C는 몇 주 사이에 바뀌지 않는다. 그래서 유가 상승분이 거의 그대로 이익에 얹히고, 유가가 10% 오르면 이익은 그 몇 배로 흔들린다 — 신고가가 생산업체에서 먼저 나온 이유다. 중국동방항공·중국남방항공에게 같은 원유는 사는 물건이다. 항공유는 영업비용의 4분의 1을 넘고, 늘어난 비용을 운임으로 넘기려면 수요와 경쟁이 허락해야 하는데 중국 대형 국유항공은 국제선 회복이 아직 덜 돼 그 힘이 약하다. P는 못 올리고 C만 오르는 구간이라 신저가로 밀린 것이다(전가 지연은 추정). 요령은 재료를 들었을 때 "누가 수혜냐"가 아니라 그 재료가 손익계산서의 위쪽(파는 가격)에 붙는지 아래쪽(사는 원가)에 붙는지를 먼저 보는 것이다. 이번 건은 다음 분기 실적에서 항공사의 연료 단가와 좌석당 운임 중 어느 쪽이 먼저 움직이는지로 확인할 수 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 08:06 KST 실행으로 미국은 8/18(화) 마감 약 3시간 후 확정치이고, 일본·홍콩·중국A는 8/18 마감분이라 전 시장 정상 갱신이다. 스크립트가 만든 index CSV의 닛케이가 8/17에서 멈춰 있어 8/18 종가는 별도 확인값(67,460.73, -2.54%)을 사용했다. ETF 44/44·지수 8/8 수집 정상이고 PER은 TradingView 12개월 선행 배수다. 중국A는 선행 PER 표본이 얇아 밸류 수치 인용을 보류했다. 회사PC 자격증명 문제로 볼트 pull이 실패해 텔레그램 적재분은 사용하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7691.76</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-0.47</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.34</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>12.36</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>26289.71</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-1.33</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>3.06</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.76</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>13.11</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6977.94</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>2.42</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>11.49</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-4.21</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-12.57</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>65.58</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>69220.25</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.74</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>5.51</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.68</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>13.82</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>37.51</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3990.3</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.19</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.43</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>5.11</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-4.13</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.54</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4725.81</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.33</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>2.77</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-2.57</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>2.07</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25471.15</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-0.71</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.62</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4739.18</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-1.77</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-0.27</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-2.18</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.08</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>-3</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-5</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2045,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2002,7 +2084,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2041,7 +2123,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2759,7 +2841,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2800,7 +2882,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2841,7 +2923,7 @@
       <c r="F45" t="n">
         <v>-1</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2882,7 +2964,7 @@
       <c r="F46" t="n">
         <v>-1</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3395,7 +3477,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3436,7 +3518,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3475,7 +3557,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3516,7 +3598,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3557,7 +3639,7 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3596,7 +3678,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3635,7 +3717,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>당일 -2.5%로 11개 섹터 중 유일한 급락. 30년물 5.32% 급등에 고멀티플 할인율 압박이 집중</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>당일 +1.6%. 신고가 12종으로 순강도 2위, 금리·유가와 무관한 방어처로 자금 유입</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.5%. 장기금리 상승이 이자마진에 우호적이나 신고가 5종으로 강도는 완만</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.3%, 1주 -2.4%로 부진. 금리 급등이 내구소비·주택 관련 수요 우려로 전이</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.3%. 3개월 -5.3%·연초대비 -5.6%로 11개 섹터 최하위 흐름 지속</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.5%. 공조·기계 5종이 신저가로 밀리며 금리민감 자본재의 약한 고리 노출</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>당일 +1.1%. 위험회피 국면에서 방어 수요, 다만 3개월 +0.3%로 추세는 아직 미약</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>11.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>당일 +1.8%, 1주 +4.5%로 전 섹터 1위. 브렌트 90달러에 신고가 14종, 연초대비 +44.4% 선두</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>44.4</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.4%. 탈렌에너지 증자 희석 우려로 -11% 급락한 개별 악재가 지수 발목</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.9%. 마틴마리에타·CRH 골재 2종 신저가로 건설 사슬 약세가 소재까지 확산</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.4%, 1개월 -1.3%. 장기금리 급등에 자산 할인율 부담이 재차 부각</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>8</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>57.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>35.9</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>49.5</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-5.1</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>당일 보합이나 1주 +5.8%로 강세 유지. 연초대비 +54.6%로 A주 13개 테마 중 1위</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>54.6</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.4%. 1주 +4.7%의 상승분을 되돌리는 조정, AI연산주 차익실현과 같은 결</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>37.6</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.4%로 A주 하위권. 루이제네트워크 -7.4% 등 통신장비 차익실현이 직접 반영</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>45.1</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.9%. 싸이리스가 A·H 동시 신저가를 내며 완성차 판매 둔화 우려가 지속</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-18.1</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.3%. 1개월 +10.8%에도 3개월 -14.7%로 되돌림 국면, 중동 긴장 반영은 제한적</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-14.7</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>10</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.5%, 1개월 +13.4%로 반등 지속. 다만 3개월 -21.0%로 낙폭 회복 초기 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.7%로 반등했으나 연초대비 -19.2%로 13개 테마 중 최하위, 소비 부진 지속</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-19.2</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.8%로 A주 1위. 지수 혼조 속 고배당 방어 수요, 차이나텔레콤 신고가와 같은 맥락</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>당일 -0.8%. 1개월 +19.0%로 A주 최고 상승폭을 낸 뒤 나오는 숨고르기</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>당일 보합. 1개월 +7.6%에도 연초대비 -17.7%로 추세 반전 근거는 아직 부족</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-12.9</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-17.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>당일 -1.5%로 A주 최약. 거래대금 둔화 우려에 증권주가 지수 하락을 주도</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>2.7</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-11.1</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>당일 보합이나 3개월 +15.6%로 A주 1위. 캉룽화청 신고가 등 위탁개발생산 강세가 뒷받침</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>당일 +0.6%로 반등. 다만 연초대비 -15.4%로 소비 회복 신호로 보기엔 이른 단계</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.4</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>11</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-3.8"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-2.7"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-6.9"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-21"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-19.2"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7637,10 +7865,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>엑손모빌(석유·가스 통합메이저): 이란 긴장으로 브렌트 90달러, 유가 강세 직접 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7689,10 +7921,10 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7745,15 +7977,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7801,15 +8033,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7853,10 +8085,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7909,15 +8141,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7959,10 +8191,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>길리어드사이언스(HIV·간질환 치료제): HIV 부문 성장과 가이던스 상향으로 투자심리 개선</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8011,15 +8247,15 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8063,15 +8299,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8115,15 +8351,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8167,10 +8403,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8223,15 +8459,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8275,10 +8511,10 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8331,10 +8567,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8387,15 +8623,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8439,15 +8675,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8491,15 +8727,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8543,15 +8779,19 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>노스롭그루먼(방산): 해군 E-2D 호크아이 설계검토 완료, 중동 긴장에 방산 재부각</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8595,15 +8835,15 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8647,15 +8887,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8703,15 +8943,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8751,15 +8991,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8803,15 +9043,15 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8859,15 +9099,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>타가리소스(천연가스 미드스트림): 엑손모빌과 퍼미안 20년 가스처리 계약·신규 플랜트 3기 발표</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8915,15 +9159,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>CRH(건자재·시멘트): 금리 급등과 주택경기 둔화 우려로 건자재 섹터 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8971,10 +9219,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9027,19 +9275,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>(전일) 세노버스에너지(캐나다 석유·가스 통합기업): 이란·호르무즈 리스크發 유가 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9083,15 +9331,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9135,10 +9383,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9187,19 +9435,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr">
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>(전일) 레볼루션메디슨스(RAS 표적 항암신약 바이오텍): 애널리스트 목표주가 잇단 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9241,15 +9489,19 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>아틀라시안(협업 소프트웨어): 4분기 실적 서프라이즈에 BofA 등 목표주가 대거 상향</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9297,15 +9549,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9349,15 +9601,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9405,10 +9657,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>마틴마리에타(골재·시멘트): 장기금리 급등으로 건설 수요 둔화 우려, 금리민감 동반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9457,14 +9713,14 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>(전일) 폭스코퍼레이션(미디어·방송): FY26 4분기 매출 28%↑, 튜비 최대 실적·월드컵 광고 효과</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9513,10 +9769,10 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9565,10 +9821,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9621,15 +9877,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9673,10 +9929,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9729,10 +9985,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9785,15 +10041,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9841,10 +10097,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9891,10 +10147,10 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9947,10 +10203,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10001,14 +10257,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>(전일) 스텔란티스(피아트·크라이슬러·푸조 보유 완성차): 후방카메라 결함 848만대 리콜</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10061,19 +10317,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 퍼미안리소시스(퍼미안분지 셰일원유 생산): 이란·호르무즈 리스크發 유가 강세 수혜</t>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>퍼미안리소시스(셰일 원유 생산): 웰스파고 목표주가 상향(26→27달러)에 유가 강세 동반</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10117,15 +10373,15 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10173,10 +10429,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10229,19 +10485,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>(전일) 롤린스(해충방제 서비스): 2분기 EPS 0.32달러로 컨센 하회·경영진 교체 우려로 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10285,10 +10541,10 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10337,15 +10593,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10393,10 +10649,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10449,15 +10705,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10499,10 +10755,14 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>탈렌에너지(원전 기반 전력 도매공급): 9.8억달러 증자 희석 우려와 목표주가 하향 겹침</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10551,10 +10811,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10603,10 +10863,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10655,15 +10915,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10711,15 +10971,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10765,10 +11025,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>매디슨에어솔루션(공조·환기 설비): 54억달러 ebm-papst 인수 발표에 희석 우려로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10819,15 +11083,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10875,15 +11139,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10931,10 +11195,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10983,19 +11251,19 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr">
+      <c r="N64" s="10" t="inlineStr">
         <is>
           <t>(전일) 데커스아웃도어(UGG·호카 신발 브랜드): 특별한 뉴스 없음(의류·신발 섹터 전반 약세 동조)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11039,15 +11307,15 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11095,15 +11363,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11147,10 +11415,10 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11203,19 +11471,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>(전일) 달링인그리디언츠(동물부산물·재생연료 원료): 2분기 사상최대 실적·자사주 10억달러 여진</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11259,10 +11527,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11315,7 +11583,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N70"/>
@@ -11421,7 +11689,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11468,14 +11736,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 미쓰비시중공업(중공업·방위산업): 방위비 증액 기대와 1분기 실적 호조 지속으로 상승</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11528,19 +11796,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 리소나홀딩스(대형 은행지주): 정부의 조기 금리인상 지지 보도로 은행주 일제 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11582,15 +11850,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시지쇼(도심 오피스 개발·임대): 10년물 2.945% 급등에 부동산 매도, 연중 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11638,10 +11910,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>미쓰이부동산(오피스·주택 개발): 금리 급등에 조달비용·자산가치 우려로 연중 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11688,19 +11964,19 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 스미토모부동산(도쿄 오피스 중심 대형 디벨로퍼): 30년물 국채금리 최고치·일본은행 추가 인상 경계로 부동산주 매도</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11744,10 +12020,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>스미토모금속광산(구리·니켈 등 비철제련): 특별한 뉴스 없음(비철·금값 강세 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11800,14 +12080,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 니혼유센(벌크·컨테이너 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11856,15 +12136,15 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11906,15 +12186,19 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>올림푸스(내시경 등 의료기기): 회계연도 실적 저점 통과 기대에 매수세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11962,15 +12246,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>치바은행(지방은행): 장기금리 상승에 따른 순이자마진 개선 기대로 매수세 유입</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12018,10 +12306,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>시즈오카파이낸셜그룹(지방은행): 장기금리 급등과 일본은행 추가 인상 기대에 은행주 매수</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12074,7 +12366,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) 가와사키기선(컨테이너선 해운): 해운 3종 동반 강세, 컨테이너 운임 기대(당일 개별뉴스 미확인)</t>
         </is>
@@ -12184,7 +12476,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12235,14 +12527,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 중지쉬촹(AI 데이터센터용 광트랜시버 1위, 최근 홍콩 상장): AI연산 수요·800G→1.6T 전환 기대, 열관리업체 지분인수 공시</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12295,19 +12587,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 코스코해운지주 H주(중국 최대 국영 컨테이너 해운): 성수기 물동량·호르무즈 운임 급등, 머스크 가이던스 2차 상향 동조</t>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>코스코해운홀딩스(컨테이너 해운): 특별한 뉴스 없음(호르무즈발 운임 강세 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12355,10 +12647,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>우시바이오로직스(바이오의약품 위탁개발생산): 신약목록 편입 기대에 업종 상승률 선두</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12411,14 +12707,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 콰이쇼우(중국 2위 숏폼동영상·라이브커머스): 전자상거래 거래액 성장 둔화 우려, 8/20 실적발표 앞두고 신저가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12471,14 +12767,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) SITC인터내셔널(아시아 역내 컨테이너 해운): 개별 뉴스 없음, 중간실적 앞둔 해운 강세 동조 추정</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12529,19 +12825,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) OOIL(오리엔트 오버시즈, 컨테이너 해운): 성수기 물동량·호르무즈 리스크로 운임 급등 수혜</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12587,10 +12883,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>싸이리스그룹(신에너지차 완성차): 원제 브랜드 판매 급감 여진, 실적 부진 우려 지속</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12643,15 +12943,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12697,15 +12997,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>중국남방항공(항공운송): 중동 긴장발 유가 급등으로 항공유 비용 부담 확대</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12751,10 +13055,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>중국철도건설(철도·인프라 시공): 특별한 뉴스 없음(수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12801,15 +13109,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12853,15 +13161,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>중국동방항공(항공운송): 중동 긴장발 유가 급등으로 항공유 비용 부담 확대</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12905,7 +13217,11 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>우시XDC(항체약물접합체 위탁개발생산): 바이오 업종 정책 훈풍에 동반 강세</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N14"/>
@@ -13011,12 +13327,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13058,10 +13374,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>차이나텔레콤(유선·이동통신 인프라): 특별한 뉴스 없음(고배당 방어주 수급 유입 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13112,14 +13432,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 우시앱텍 A주(위탁연구개발·위탁생산): 상반기 매출 +39%·순이익 +29% 서프라이즈, 미국 규제 리스크 완화</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13168,14 +13488,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운지주 A주(중국 최대 국영 컨테이너 해운): 호르무즈 운임 급등·머스크 가이던스 상향에 해운주 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13224,19 +13544,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 화뎬신에너지(화뎬그룹 산하 신재생 발전사): 특별한 뉴스 없음(신재생 발전주 약세 흐름 속 신저가)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13282,15 +13602,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>루이제네트워크(네트워크 장비·AI연산 인프라): 장중 신고가 후 AI연산 차익실현에 급락</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13336,15 +13660,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>싸이리스그룹(신에너지차 완성차): 원제 7월 판매 전년비 51% 급감 여진으로 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13392,15 +13720,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>캉룽화청(신약 위탁개발생산): 일라이릴리 비만치료제 수주 확보, 이달 업종 상승률 1위</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13446,7 +13778,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>레이턴테크놀로지(적외선 열화상 센서): 상반기 순이익 급증 모멘텀에 반도체장비 테마 편승</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N9"/>
